--- a/medical_surveys_questionnaires/040_physician_work_setting_assessment--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/040_physician_work_setting_assessment--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Burnout Other</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Burnout Reasons Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Burnout Prevention Strategies Other</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>burnout_prevention_strategies_other</t>
+          <t>burnout_prevention_strategies_other_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>If other, please specify</t>
+          <t>Burnout Prevention Strategies Other 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'primary_care'}</t>
+          <t>primary_care</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Primary Care'}</t>
+          <t>Primary Care</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'specialty_clinic'}</t>
+          <t>specialty_clinic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Specialty Clinic'}</t>
+          <t>Specialty Clinic</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'heavy'}</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Heavy'}</t>
+          <t>Heavy</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'high_work_hours'}</t>
+          <t>high_work_hours</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'High work hours'}</t>
+          <t>High work hours</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'high_patient_demand'}</t>
+          <t>high_patient_demand</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'High patient demand'}</t>
+          <t>High patient demand</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'high_expectations'}</t>
+          <t>high_expectations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'High expectations'}</t>
+          <t>High expectations</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Time management'}</t>
+          <t>Time management</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'self-care'}</t>
+          <t>self-care</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Self-care'}</t>
+          <t>Self-care</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'support_from_colleagues'}</t>
+          <t>support_from_colleagues</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Support from colleagues'}</t>
+          <t>Support from colleagues</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
